--- a/data/Store_Master.xlsx
+++ b/data/Store_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://apparelme-my.sharepoint.com/personal/138925_appareluae_com/Documents/F&amp;B Sales Dashboard - Project/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="182" documentId="8_{DB8E79A2-F353-468B-8FC9-094421811B91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{30A5487D-B248-4AFD-B977-DBFEAA310BBB}"/>
+  <xr:revisionPtr revIDLastSave="183" documentId="8_{DB8E79A2-F353-468B-8FC9-094421811B91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{63500E51-6726-4C7F-B2B5-02CBB65DBF8D}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{7D4174F8-86A5-4506-B54F-CFAB4FB5A869}"/>
   </bookViews>
@@ -786,10 +786,10 @@
     <t>status</t>
   </si>
   <si>
-    <t>Active</t>
-  </si>
-  <si>
-    <t>InActive</t>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>no</t>
   </si>
 </sst>
 </file>

--- a/data/Store_Master.xlsx
+++ b/data/Store_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://apparelme-my.sharepoint.com/personal/138925_appareluae_com/Documents/F&amp;B Sales Dashboard - Project/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="184" documentId="8_{DB8E79A2-F353-468B-8FC9-094421811B91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{83C872DF-0376-41B1-91E9-3E6BC94DB5B8}"/>
+  <xr:revisionPtr revIDLastSave="185" documentId="8_{DB8E79A2-F353-468B-8FC9-094421811B91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{44929D67-3021-4040-BD91-778DC1E9CEF8}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{7D4174F8-86A5-4506-B54F-CFAB4FB5A869}"/>
+    <workbookView xWindow="9670" yWindow="2110" windowWidth="11760" windowHeight="6160" xr2:uid="{7D4174F8-86A5-4506-B54F-CFAB4FB5A869}"/>
   </bookViews>
   <sheets>
     <sheet name="Store_Master_tbl" sheetId="1" r:id="rId1"/>
@@ -765,9 +765,6 @@
     <t>store_name</t>
   </si>
   <si>
-    <t>brand_Code</t>
-  </si>
-  <si>
     <t>country_code</t>
   </si>
   <si>
@@ -790,6 +787,9 @@
   </si>
   <si>
     <t>no</t>
+  </si>
+  <si>
+    <t>brand_code</t>
   </si>
 </sst>
 </file>
@@ -1166,28 +1166,28 @@
         <v>239</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>240</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>242</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
@@ -1210,7 +1210,7 @@
         <v>229</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H2" s="1">
         <v>6101026855</v>
@@ -1239,7 +1239,7 @@
         <v>229</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H3" s="1">
         <v>6101027080</v>
@@ -1268,7 +1268,7 @@
         <v>229</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H4" s="1">
         <v>6101336857</v>
@@ -1297,7 +1297,7 @@
         <v>229</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H5" s="1">
         <v>6101043251</v>
@@ -1326,7 +1326,7 @@
         <v>229</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H6" s="1">
         <v>6101245019</v>
@@ -1355,7 +1355,7 @@
         <v>229</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H7" s="1">
         <v>6101246409</v>
@@ -1384,7 +1384,7 @@
         <v>229</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H8" s="1">
         <v>6101246811</v>
@@ -1413,7 +1413,7 @@
         <v>229</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H9" s="1">
         <v>6101046856</v>
@@ -1442,7 +1442,7 @@
         <v>229</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H10" s="1">
         <v>6101047034</v>
@@ -1471,7 +1471,7 @@
         <v>229</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H11" s="1">
         <v>6101063273</v>
@@ -1500,7 +1500,7 @@
         <v>229</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H12" s="1">
         <v>6101174581</v>
@@ -1529,7 +1529,7 @@
         <v>229</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H13" s="1">
         <v>6101083292</v>
@@ -1558,7 +1558,7 @@
         <v>230</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H14" s="1">
         <v>3101316894</v>
@@ -1587,7 +1587,7 @@
         <v>230</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H15" s="1">
         <v>3101417382</v>
@@ -1616,7 +1616,7 @@
         <v>230</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H16" s="1">
         <v>3101027352</v>
@@ -1645,7 +1645,7 @@
         <v>230</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H17" s="1">
         <v>3101437288</v>
@@ -1674,7 +1674,7 @@
         <v>230</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H18" s="1">
         <v>3101437297</v>
@@ -1703,7 +1703,7 @@
         <v>230</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H19" s="1">
         <v>3101046975</v>
@@ -1732,7 +1732,7 @@
         <v>230</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H20" s="1">
         <v>3101156803</v>
@@ -1761,7 +1761,7 @@
         <v>230</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H21" s="1">
         <v>3101376517</v>
@@ -1790,7 +1790,7 @@
         <v>230</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H22" s="1">
         <v>3101376885</v>
@@ -1819,7 +1819,7 @@
         <v>230</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H23" s="1">
         <v>3101376886</v>
@@ -1848,7 +1848,7 @@
         <v>230</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H24" s="1">
         <v>3101276971</v>
@@ -1877,7 +1877,7 @@
         <v>230</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H25" s="1">
         <v>3101276972</v>
@@ -1906,7 +1906,7 @@
         <v>230</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H26" s="1">
         <v>3101276980</v>
@@ -1935,7 +1935,7 @@
         <v>230</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H27" s="1">
         <v>3101277289</v>
@@ -1964,7 +1964,7 @@
         <v>230</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H28" s="1">
         <v>3101377353</v>
@@ -1993,7 +1993,7 @@
         <v>230</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H29" s="1">
         <v>3101377354</v>
@@ -2022,7 +2022,7 @@
         <v>230</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H30" s="1">
         <v>3101396789</v>
@@ -2051,7 +2051,7 @@
         <v>231</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H31" s="1">
         <v>5101315524</v>
@@ -2080,7 +2080,7 @@
         <v>231</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H32" s="1">
         <v>5101315920</v>
@@ -2109,7 +2109,7 @@
         <v>231</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H33" s="1">
         <v>5101526589</v>
@@ -2138,7 +2138,7 @@
         <v>231</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H34" s="1">
         <v>5101103133</v>
@@ -2167,7 +2167,7 @@
         <v>231</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H35" s="1">
         <v>5101133161</v>
@@ -2196,7 +2196,7 @@
         <v>231</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H36" s="1">
         <v>5101135842</v>
@@ -2225,7 +2225,7 @@
         <v>231</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H37" s="1">
         <v>5101045507</v>
@@ -2254,7 +2254,7 @@
         <v>231</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H38" s="1">
         <v>5101045041</v>
@@ -2283,7 +2283,7 @@
         <v>231</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H39" s="1">
         <v>5101045552</v>
@@ -2312,7 +2312,7 @@
         <v>231</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H40" s="1">
         <v>5101355846</v>
@@ -2341,7 +2341,7 @@
         <v>231</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H41" s="1">
         <v>5101163673</v>
@@ -2370,7 +2370,7 @@
         <v>231</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H42" s="1">
         <v>5101164140</v>
@@ -2399,7 +2399,7 @@
         <v>231</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H43" s="1">
         <v>5101164768</v>
@@ -2428,7 +2428,7 @@
         <v>231</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H44" s="1">
         <v>5101165841</v>
@@ -2457,7 +2457,7 @@
         <v>231</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H45" s="1">
         <v>5101073103</v>
@@ -2486,7 +2486,7 @@
         <v>231</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H46" s="1">
         <v>5101173780</v>
@@ -2515,7 +2515,7 @@
         <v>231</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H47" s="1">
         <v>5101095308</v>
@@ -2544,7 +2544,7 @@
         <v>231</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H48" s="1">
         <v>5101295502</v>
@@ -2573,7 +2573,7 @@
         <v>231</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H49" s="1">
         <v>5101295503</v>
@@ -2602,7 +2602,7 @@
         <v>231</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H50" s="1">
         <v>5101095891</v>
@@ -2631,7 +2631,7 @@
         <v>232</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H51" s="1">
         <v>2271116119</v>
@@ -2660,7 +2660,7 @@
         <v>232</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H52" s="1">
         <v>2181516847</v>
@@ -2689,7 +2689,7 @@
         <v>232</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H53" s="1">
         <v>2181517313</v>
@@ -2718,7 +2718,7 @@
         <v>232</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H54" s="1">
         <v>2181817332</v>
@@ -2747,7 +2747,7 @@
         <v>232</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H55" s="1">
         <v>2271817368</v>
@@ -2776,7 +2776,7 @@
         <v>232</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H56" s="1">
         <v>2271817369</v>
@@ -2805,7 +2805,7 @@
         <v>232</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H57" s="1">
         <v>2271826334</v>
@@ -2834,7 +2834,7 @@
         <v>232</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H58" s="1">
         <v>2272226649</v>
@@ -2863,7 +2863,7 @@
         <v>232</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H59" s="1">
         <v>2271226731</v>
@@ -2892,7 +2892,7 @@
         <v>232</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H60" s="1">
         <v>2271126872</v>
@@ -2921,7 +2921,7 @@
         <v>232</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H61" s="1">
         <v>2271627075</v>
@@ -2950,7 +2950,7 @@
         <v>232</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H62" s="1">
         <v>2272427108</v>
@@ -2979,7 +2979,7 @@
         <v>232</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H63" s="1">
         <v>2272427109</v>
@@ -3008,7 +3008,7 @@
         <v>232</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H64" s="1">
         <v>2272427166</v>
@@ -3037,7 +3037,7 @@
         <v>232</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H65" s="1">
         <v>2272427167</v>
@@ -3066,7 +3066,7 @@
         <v>232</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H66" s="1">
         <v>2271127169</v>
@@ -3095,7 +3095,7 @@
         <v>232</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H67" s="1">
         <v>2271627220</v>
@@ -3124,7 +3124,7 @@
         <v>232</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H68" s="1">
         <v>2271627247</v>
@@ -3153,7 +3153,7 @@
         <v>232</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H69" s="1">
         <v>2271127291</v>
@@ -3182,7 +3182,7 @@
         <v>232</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H70" s="1">
         <v>2221227313</v>
@@ -3211,7 +3211,7 @@
         <v>232</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H71" s="1">
         <v>2272527392</v>
@@ -3240,7 +3240,7 @@
         <v>232</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H72" s="1">
         <v>2271035438</v>
@@ -3269,7 +3269,7 @@
         <v>232</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H73" s="1">
         <v>2271035439</v>
@@ -3298,7 +3298,7 @@
         <v>232</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H74" s="1">
         <v>2272136292</v>
@@ -3327,7 +3327,7 @@
         <v>232</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H75" s="1">
         <v>2271306413</v>
@@ -3356,7 +3356,7 @@
         <v>232</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H76" s="1">
         <v>2231036674</v>
@@ -3385,7 +3385,7 @@
         <v>232</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H77" s="1">
         <v>2181736678</v>
@@ -3414,7 +3414,7 @@
         <v>232</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H78" s="1">
         <v>2181736679</v>
@@ -3443,7 +3443,7 @@
         <v>232</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H79" s="1">
         <v>2271306797</v>
@@ -3472,7 +3472,7 @@
         <v>232</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H80" s="1">
         <v>2271036871</v>
@@ -3501,7 +3501,7 @@
         <v>232</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H81" s="1">
         <v>2271307072</v>
@@ -3530,7 +3530,7 @@
         <v>232</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H82" s="1">
         <v>2181737116</v>
@@ -3559,7 +3559,7 @@
         <v>232</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H83" s="1">
         <v>2271037241</v>
@@ -3588,7 +3588,7 @@
         <v>232</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H84" s="1">
         <v>2221237420</v>
@@ -3617,7 +3617,7 @@
         <v>232</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H85" s="1">
         <v>2271645857</v>
@@ -3646,7 +3646,7 @@
         <v>232</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H86" s="1">
         <v>2271646295</v>
@@ -3675,7 +3675,7 @@
         <v>232</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H87" s="1">
         <v>2272146732</v>
@@ -3704,7 +3704,7 @@
         <v>232</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H88" s="1">
         <v>2271747425</v>
@@ -3733,7 +3733,7 @@
         <v>232</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H89" s="1">
         <v>2271152654</v>
@@ -3762,7 +3762,7 @@
         <v>232</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H90" s="1">
         <v>2271256414</v>
@@ -3791,7 +3791,7 @@
         <v>232</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H91" s="1">
         <v>2271056543</v>
@@ -3820,7 +3820,7 @@
         <v>232</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H92" s="1">
         <v>2271356826</v>
@@ -3849,7 +3849,7 @@
         <v>232</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H93" s="1">
         <v>2181756874</v>
@@ -3878,7 +3878,7 @@
         <v>232</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H94" s="1">
         <v>2231057430</v>
@@ -3907,7 +3907,7 @@
         <v>232</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H95" s="1">
         <v>2231057431</v>
@@ -3936,7 +3936,7 @@
         <v>232</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H96" s="1">
         <v>2231057432</v>
@@ -3965,7 +3965,7 @@
         <v>232</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H97" s="1">
         <v>2151164995</v>
@@ -3994,7 +3994,7 @@
         <v>232</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H98" s="1">
         <v>2151164996</v>
@@ -4023,7 +4023,7 @@
         <v>232</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H99" s="1">
         <v>2151166876</v>
@@ -4052,7 +4052,7 @@
         <v>232</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H100" s="1">
         <v>2272367037</v>
@@ -4081,7 +4081,7 @@
         <v>232</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H101" s="1">
         <v>2221167091</v>
@@ -4110,7 +4110,7 @@
         <v>232</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H102" s="1">
         <v>2272367126</v>
@@ -4139,7 +4139,7 @@
         <v>232</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H103" s="1">
         <v>2271167242</v>
@@ -4168,7 +4168,7 @@
         <v>232</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H104" s="1">
         <v>2272467251</v>
@@ -4197,7 +4197,7 @@
         <v>232</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H105" s="1">
         <v>2272467255</v>
@@ -4226,7 +4226,7 @@
         <v>232</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H106" s="1">
         <v>2181767257</v>
@@ -4255,7 +4255,7 @@
         <v>232</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H107" s="1">
         <v>2181767258</v>
@@ -4284,7 +4284,7 @@
         <v>232</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H108" s="1">
         <v>2181767259</v>
@@ -4313,7 +4313,7 @@
         <v>232</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H109" s="1">
         <v>2181767260</v>
@@ -4342,7 +4342,7 @@
         <v>232</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H110" s="1">
         <v>2181767261</v>
@@ -4371,7 +4371,7 @@
         <v>232</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H111" s="1">
         <v>2272467280</v>
@@ -4400,7 +4400,7 @@
         <v>232</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H112" s="1">
         <v>2231167391</v>
@@ -4429,7 +4429,7 @@
         <v>232</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H113" s="1">
         <v>2272567421</v>
@@ -4458,7 +4458,7 @@
         <v>232</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H114" s="1">
         <v>2272567422</v>
@@ -4487,7 +4487,7 @@
         <v>232</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H115" s="1">
         <v>2271875679</v>
@@ -4516,7 +4516,7 @@
         <v>232</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H116" s="1">
         <v>2271875839</v>
@@ -4545,7 +4545,7 @@
         <v>232</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H117" s="1">
         <v>2271875840</v>
@@ -4574,7 +4574,7 @@
         <v>232</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H118" s="1">
         <v>2271976291</v>
@@ -4603,7 +4603,7 @@
         <v>232</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H119" s="1">
         <v>2181276354</v>
@@ -4632,7 +4632,7 @@
         <v>232</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H120" s="1">
         <v>2271876873</v>
@@ -4661,7 +4661,7 @@
         <v>232</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H121" s="1">
         <v>2181276875</v>
@@ -4690,7 +4690,7 @@
         <v>232</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H122" s="1">
         <v>2271876948</v>
@@ -4719,7 +4719,7 @@
         <v>232</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H123" s="1">
         <v>2272377042</v>
@@ -4748,7 +4748,7 @@
         <v>232</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H124" s="1">
         <v>2181577093</v>
@@ -4777,7 +4777,7 @@
         <v>232</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H125" s="1">
         <v>2181777267</v>
@@ -4806,7 +4806,7 @@
         <v>232</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H126" s="1">
         <v>2272477311</v>
@@ -4835,7 +4835,7 @@
         <v>232</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H127" s="1">
         <v>2181277329</v>
@@ -4864,7 +4864,7 @@
         <v>232</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H128" s="1">
         <v>2201077343</v>
@@ -4893,7 +4893,7 @@
         <v>232</v>
       </c>
       <c r="G129" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H129" s="1">
         <v>2201077418</v>
@@ -4922,7 +4922,7 @@
         <v>232</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H130" s="1">
         <v>2181787275</v>
@@ -4951,7 +4951,7 @@
         <v>232</v>
       </c>
       <c r="G131" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H131" s="1">
         <v>2272487312</v>
@@ -4980,7 +4980,7 @@
         <v>232</v>
       </c>
       <c r="G132" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H132" s="1">
         <v>2151287330</v>
@@ -5009,7 +5009,7 @@
         <v>232</v>
       </c>
       <c r="G133" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H133" s="1">
         <v>2271687493</v>
@@ -5038,7 +5038,7 @@
         <v>232</v>
       </c>
       <c r="G134" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H134" s="1">
         <v>2271687494</v>
@@ -5067,7 +5067,7 @@
         <v>232</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H135" s="1">
         <v>2271687504</v>
@@ -5096,7 +5096,7 @@
         <v>232</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H136" s="1">
         <v>2272497331</v>
@@ -5125,7 +5125,7 @@
         <v>232</v>
       </c>
       <c r="G137" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H137" s="1">
         <v>2272497423</v>
@@ -5154,7 +5154,7 @@
         <v>232</v>
       </c>
       <c r="G138" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H138" s="1">
         <v>2272497424</v>
@@ -5183,7 +5183,7 @@
         <v>233</v>
       </c>
       <c r="G139" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H139" s="1">
         <v>1131305742</v>
@@ -5212,7 +5212,7 @@
         <v>233</v>
       </c>
       <c r="G140" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H140" s="1">
         <v>1131835791</v>
@@ -5241,7 +5241,7 @@
         <v>233</v>
       </c>
       <c r="G141" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H141" s="1">
         <v>1131764960</v>
@@ -5270,7 +5270,7 @@
         <v>233</v>
       </c>
       <c r="G142" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H142" s="1">
         <v>1101011010</v>
@@ -5299,7 +5299,7 @@
         <v>233</v>
       </c>
       <c r="G143" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H143" s="1">
         <v>1131611935</v>
@@ -5328,7 +5328,7 @@
         <v>233</v>
       </c>
       <c r="G144" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H144" s="1">
         <v>1141012033</v>
@@ -5357,7 +5357,7 @@
         <v>233</v>
       </c>
       <c r="G145" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H145" s="1">
         <v>1161012156</v>
@@ -5386,7 +5386,7 @@
         <v>233</v>
       </c>
       <c r="G146" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H146" s="1">
         <v>1131916146</v>
@@ -5415,7 +5415,7 @@
         <v>233</v>
       </c>
       <c r="G147" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H147" s="1">
         <v>1131916193</v>
@@ -5444,7 +5444,7 @@
         <v>233</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H148" s="1">
         <v>1131916194</v>
@@ -5473,7 +5473,7 @@
         <v>233</v>
       </c>
       <c r="G149" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H149" s="1">
         <v>1131016512</v>
@@ -5502,7 +5502,7 @@
         <v>233</v>
       </c>
       <c r="G150" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H150" s="1">
         <v>1132016542</v>
@@ -5531,7 +5531,7 @@
         <v>233</v>
       </c>
       <c r="G151" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H151" s="1">
         <v>1132116991</v>
@@ -5560,7 +5560,7 @@
         <v>233</v>
       </c>
       <c r="G152" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H152" s="1">
         <v>1171022215</v>
@@ -5589,7 +5589,7 @@
         <v>233</v>
       </c>
       <c r="G153" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H153" s="1">
         <v>1101124586</v>
@@ -5618,7 +5618,7 @@
         <v>233</v>
       </c>
       <c r="G154" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H154" s="1">
         <v>1101124587</v>
@@ -5647,7 +5647,7 @@
         <v>233</v>
       </c>
       <c r="G155" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H155" s="1">
         <v>1101425844</v>
@@ -5676,7 +5676,7 @@
         <v>233</v>
       </c>
       <c r="G156" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H156" s="1">
         <v>1111025924</v>
@@ -5705,7 +5705,7 @@
         <v>233</v>
       </c>
       <c r="G157" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H157" s="1">
         <v>1101426569</v>
@@ -5734,7 +5734,7 @@
         <v>233</v>
       </c>
       <c r="G158" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H158" s="1">
         <v>1101126573</v>
@@ -5763,7 +5763,7 @@
         <v>233</v>
       </c>
       <c r="G159" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H159" s="1">
         <v>1101426685</v>
@@ -5792,7 +5792,7 @@
         <v>233</v>
       </c>
       <c r="G160" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H160" s="1">
         <v>1101327008</v>
@@ -5821,7 +5821,7 @@
         <v>233</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H161" s="1">
         <v>1131431821</v>
@@ -5850,7 +5850,7 @@
         <v>233</v>
       </c>
       <c r="G162" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H162" s="1">
         <v>1161032176</v>
@@ -5879,7 +5879,7 @@
         <v>233</v>
       </c>
       <c r="G163" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H163" s="1">
         <v>1131835789</v>
@@ -5908,7 +5908,7 @@
         <v>233</v>
       </c>
       <c r="G164" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H164" s="1">
         <v>1131835790</v>
@@ -5937,7 +5937,7 @@
         <v>233</v>
       </c>
       <c r="G165" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H165" s="1">
         <v>1131835792</v>
@@ -5966,7 +5966,7 @@
         <v>233</v>
       </c>
       <c r="G166" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H166" s="1">
         <v>1131835874</v>
@@ -5995,7 +5995,7 @@
         <v>233</v>
       </c>
       <c r="G167" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H167" s="1">
         <v>1131136204</v>
@@ -6024,7 +6024,7 @@
         <v>233</v>
       </c>
       <c r="G168" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H168" s="1">
         <v>1101436374</v>
@@ -6053,7 +6053,7 @@
         <v>233</v>
       </c>
       <c r="G169" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H169" s="1">
         <v>1101241176</v>
@@ -6082,7 +6082,7 @@
         <v>233</v>
       </c>
       <c r="G170" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H170" s="1">
         <v>1111041236</v>
@@ -6111,7 +6111,7 @@
         <v>233</v>
       </c>
       <c r="G171" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H171" s="1">
         <v>1131341759</v>
@@ -6140,7 +6140,7 @@
         <v>233</v>
       </c>
       <c r="G172" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H172" s="1">
         <v>1131304336</v>
@@ -6169,7 +6169,7 @@
         <v>233</v>
       </c>
       <c r="G173" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H173" s="1">
         <v>1131846723</v>
@@ -6198,7 +6198,7 @@
         <v>233</v>
       </c>
       <c r="G174" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H174" s="1">
         <v>1131151593</v>
@@ -6227,7 +6227,7 @@
         <v>233</v>
       </c>
       <c r="G175" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H175" s="1">
         <v>1121054515</v>
@@ -6256,7 +6256,7 @@
         <v>233</v>
       </c>
       <c r="G176" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H176" s="1">
         <v>1121054516</v>
@@ -6285,7 +6285,7 @@
         <v>233</v>
       </c>
       <c r="G177" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H177" s="1">
         <v>1131856145</v>
@@ -6314,7 +6314,7 @@
         <v>233</v>
       </c>
       <c r="G178" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H178" s="1">
         <v>1121056722</v>
@@ -6343,7 +6343,7 @@
         <v>233</v>
       </c>
       <c r="G179" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H179" s="1">
         <v>1101456822</v>
@@ -6372,7 +6372,7 @@
         <v>233</v>
       </c>
       <c r="G180" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H180" s="1">
         <v>1101456823</v>
@@ -6401,7 +6401,7 @@
         <v>233</v>
       </c>
       <c r="G181" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H181" s="1">
         <v>1101457286</v>
@@ -6430,7 +6430,7 @@
         <v>233</v>
       </c>
       <c r="G182" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H182" s="1">
         <v>1131261725</v>
@@ -6459,7 +6459,7 @@
         <v>233</v>
       </c>
       <c r="G183" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H183" s="1">
         <v>1131361771</v>
@@ -6488,7 +6488,7 @@
         <v>233</v>
       </c>
       <c r="G184" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H184" s="1">
         <v>1131264753</v>
@@ -6517,7 +6517,7 @@
         <v>233</v>
       </c>
       <c r="G185" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H185" s="1">
         <v>1161066526</v>
@@ -6546,7 +6546,7 @@
         <v>233</v>
       </c>
       <c r="G186" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H186" s="1">
         <v>1161066527</v>
@@ -6575,7 +6575,7 @@
         <v>233</v>
       </c>
       <c r="G187" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H187" s="1">
         <v>1131366724</v>
@@ -6604,7 +6604,7 @@
         <v>233</v>
       </c>
       <c r="G188" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H188" s="1">
         <v>1161066735</v>
@@ -6633,7 +6633,7 @@
         <v>233</v>
       </c>
       <c r="G189" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H189" s="1">
         <v>1101466896</v>
@@ -6662,7 +6662,7 @@
         <v>233</v>
       </c>
       <c r="G190" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H190" s="1">
         <v>1131267032</v>
@@ -6691,7 +6691,7 @@
         <v>233</v>
       </c>
       <c r="G191" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H191" s="1">
         <v>1141067033</v>
@@ -6720,7 +6720,7 @@
         <v>233</v>
       </c>
       <c r="G192" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H192" s="1">
         <v>1131071340</v>
@@ -6749,7 +6749,7 @@
         <v>233</v>
       </c>
       <c r="G193" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H193" s="1">
         <v>1131471852</v>
@@ -6778,7 +6778,7 @@
         <v>233</v>
       </c>
       <c r="G194" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H194" s="1">
         <v>1131081352</v>
@@ -6807,7 +6807,7 @@
         <v>233</v>
       </c>
       <c r="G195" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H195" s="1">
         <v>1131181630</v>
@@ -6836,7 +6836,7 @@
         <v>233</v>
       </c>
       <c r="G196" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H196" s="1">
         <v>1131185785</v>
@@ -6865,7 +6865,7 @@
         <v>233</v>
       </c>
       <c r="G197" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H197" s="1">
         <v>1132086787</v>
@@ -6894,7 +6894,7 @@
         <v>233</v>
       </c>
       <c r="G198" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H198" s="1">
         <v>1131287152</v>
@@ -6923,7 +6923,7 @@
         <v>233</v>
       </c>
       <c r="G199" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H199" s="1">
         <v>1131887268</v>
@@ -6952,7 +6952,7 @@
         <v>233</v>
       </c>
       <c r="G200" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H200" s="1">
         <v>1101487389</v>
@@ -6981,7 +6981,7 @@
         <v>233</v>
       </c>
       <c r="G201" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H201" s="1">
         <v>1131487482</v>
@@ -7010,7 +7010,7 @@
         <v>233</v>
       </c>
       <c r="G202" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H202" s="1">
         <v>1101091055</v>
@@ -7039,7 +7039,7 @@
         <v>233</v>
       </c>
       <c r="G203" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H203" s="1">
         <v>1131191672</v>
@@ -7068,7 +7068,7 @@
         <v>233</v>
       </c>
       <c r="G204" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H204" s="1">
         <v>1131391800</v>
@@ -7097,7 +7097,7 @@
         <v>233</v>
       </c>
       <c r="G205" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H205" s="1">
         <v>1171092294</v>
@@ -7126,7 +7126,7 @@
         <v>233</v>
       </c>
       <c r="G206" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H206" s="1">
         <v>1171094514</v>
@@ -7155,7 +7155,7 @@
         <v>233</v>
       </c>
       <c r="G207" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H207" s="1">
         <v>1131795870</v>
@@ -7184,7 +7184,7 @@
         <v>233</v>
       </c>
       <c r="G208" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H208" s="1">
         <v>1101295896</v>
@@ -7213,7 +7213,7 @@
         <v>233</v>
       </c>
       <c r="G209" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H209" s="1">
         <v>1132096824</v>
@@ -7242,7 +7242,7 @@
         <v>234</v>
       </c>
       <c r="G210" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H210" s="1">
         <v>4101416315</v>
@@ -7271,7 +7271,7 @@
         <v>234</v>
       </c>
       <c r="G211" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H211" s="1">
         <v>4101416318</v>
@@ -7300,7 +7300,7 @@
         <v>234</v>
       </c>
       <c r="G212" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H212" s="1">
         <v>4101416351</v>
@@ -7329,7 +7329,7 @@
         <v>234</v>
       </c>
       <c r="G213" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H213" s="1">
         <v>4101316940</v>
@@ -7358,7 +7358,7 @@
         <v>234</v>
       </c>
       <c r="G214" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H214" s="1">
         <v>4101517194</v>
@@ -7387,7 +7387,7 @@
         <v>234</v>
       </c>
       <c r="G215" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H215" s="1">
         <v>4101527284</v>
@@ -7416,7 +7416,7 @@
         <v>234</v>
       </c>
       <c r="G216" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H216" s="1">
         <v>4101527340</v>
@@ -7445,7 +7445,7 @@
         <v>234</v>
       </c>
       <c r="G217" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H217" s="1">
         <v>4101136548</v>
@@ -7474,7 +7474,7 @@
         <v>234</v>
       </c>
       <c r="G218" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H218" s="1">
         <v>4101537285</v>
@@ -7503,7 +7503,7 @@
         <v>234</v>
       </c>
       <c r="G219" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H219" s="1">
         <v>4101056360</v>
@@ -7532,7 +7532,7 @@
         <v>234</v>
       </c>
       <c r="G220" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H220" s="1">
         <v>4101457195</v>
@@ -7561,7 +7561,7 @@
         <v>234</v>
       </c>
       <c r="G221" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H221" s="1">
         <v>4101376299</v>
@@ -7590,7 +7590,7 @@
         <v>234</v>
       </c>
       <c r="G222" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H222" s="1">
         <v>4101477012</v>
@@ -7619,7 +7619,7 @@
         <v>234</v>
       </c>
       <c r="G223" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H223" s="1">
         <v>4101486941</v>
@@ -7648,7 +7648,7 @@
         <v>234</v>
       </c>
       <c r="G224" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H224" s="1">
         <v>4101296825</v>
@@ -7677,7 +7677,7 @@
         <v>234</v>
       </c>
       <c r="G225" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H225" s="1">
         <v>4101297103</v>
@@ -7706,7 +7706,7 @@
         <v>234</v>
       </c>
       <c r="G226" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H226" s="1">
         <v>4101097402</v>
